--- a/data/review/hkm037-item1-2026-10-23/item1-w-decisions.xlsx
+++ b/data/review/hkm037-item1-2026-10-23/item1-w-decisions.xlsx
@@ -810,8 +810,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/a7119cfe-7668-488f-853f-a9a700f1ea6c/1</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -901,8 +909,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/13445632-e42b-4576-a671-a9a700f175f6/1</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1012,8 +1028,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/a98158eb-927b-4f8c-a9ff-a9a700f21e78/1</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1110,8 +1134,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/796a6587-8da2-4583-8603-ac4500d5b8bc/1</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1186,8 +1218,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/62d14b10-5bee-46e9-870a-a9a700f19762/1</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1264,8 +1304,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/62d14b10-5bee-46e9-870a-a9a700f19762/1</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1340,8 +1388,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/87e36287-f62c-4006-b677-a9a700f20677/1</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1419,8 +1475,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/16c49913-599f-406b-b016-a9a700f172c9/1</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1494,8 +1558,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/e7bd6fcc-c29c-4696-8032-aae9009b113a/1</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1569,8 +1641,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/fad7b0d1-e536-46ea-8202-a9a700f28b03/1</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1644,8 +1724,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/64aee787-4618-4979-b4d8-a9a700f1c647/1</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1720,8 +1808,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8ca91427-5be7-4807-80ae-adc700a97f0d/1</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1797,8 +1893,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/90b81287-baab-4f66-a9c1-a9a700f2ce78/1</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1874,8 +1978,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8ff3cd90-e466-4bf9-a071-a9a700f2a70d/1</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1950,8 +2062,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8ff3cd90-e466-4bf9-a071-a9a700f2a70d/1</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2039,8 +2159,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8ff3cd90-e466-4bf9-a071-a9a700f2a70d/1</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2116,8 +2244,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/0838afd4-ca76-4b4a-b1d1-a9a700f22afd/1</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2194,8 +2330,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/7017dc70-15bb-4137-b87d-a9a700f1b950/1</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2280,8 +2424,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/7017dc70-15bb-4137-b87d-a9a700f1b950/1</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2356,8 +2508,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/e36e899b-f29b-4db0-8b71-a9a700f23065/1</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2435,8 +2595,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/85364e57-c01e-41ba-8def-a9a700f183e9/1</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2511,8 +2679,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/85364e57-c01e-41ba-8def-a9a700f183e9/1</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2587,8 +2763,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/cad66e4d-38d3-4baa-8049-a9a700f1e7a8/1</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2663,8 +2847,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/cad66e4d-38d3-4baa-8049-a9a700f1e7a8/1</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2741,8 +2933,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/cabff788-438d-4003-be74-a9a700f2bcde/1</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2826,8 +3026,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/753d7ffc-5e18-4f36-818d-a9a700f213a1/1</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2902,8 +3110,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/e4436403-31ee-439c-bac4-a9a700f2a17d/1</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2978,8 +3194,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/e4436403-31ee-439c-bac4-a9a700f2a17d/1</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3057,8 +3281,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/9b461caf-dc11-46bd-a8fd-ac74009a8724/1</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3137,8 +3369,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/9b461caf-dc11-46bd-a8fd-ac74009a8724/1</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3214,8 +3454,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/9b461caf-dc11-46bd-a8fd-ac74009a8724/1</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3291,8 +3539,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/9b461caf-dc11-46bd-a8fd-ac74009a8724/1</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3368,8 +3624,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3447,8 +3711,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3532,8 +3804,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3619,8 +3899,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3695,8 +3983,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3779,8 +4075,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3855,8 +4159,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3932,8 +4244,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4008,8 +4328,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -4084,8 +4412,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4161,8 +4497,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/23576008-1ce4-4685-ac3e-a9a700f2cb02/1</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4361,8 +4705,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/903dafd6-34ee-441e-b104-a9fc00a60c78/1</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4436,8 +4788,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/0ad8fc8e-73f8-48b6-9c5b-a9a700f2974b/1</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4511,8 +4871,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/0ad8fc8e-73f8-48b6-9c5b-a9a700f2974b/1</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4586,8 +4954,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/0ad8fc8e-73f8-48b6-9c5b-a9a700f2974b/1</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4661,8 +5037,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/0ad8fc8e-73f8-48b6-9c5b-a9a700f2974b/1</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4736,8 +5120,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/0ad8fc8e-73f8-48b6-9c5b-a9a700f2974b/1</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -4814,8 +5206,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/85364e57-c01e-41ba-8def-a9a700f183e9/1</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5011,8 +5411,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5221,8 +5629,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/5329f61e-2ad8-42b8-8592-a9a700f298d1/1</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القراران 693/2 و123 يضيفان «ممثل من وزارة الطاقة» و«ممثل من الهيئة العامة لعقارات الدولة» دون تحديد موضع ولا رقم بند، فلا يمكن ترقيم القائمة (1-10). draft_text = نص القرار 241 بعد إحلال 693/1 (وزير ال)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5323,8 +5739,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/1169b2b7-4e7d-4775-86b0-a9a700f2841e/1</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 151 يضيف «مدير الإدارة العامة للخدمات الطبية في رئاسة أمن الدولة» دون موضع ولا رقم بند؛ وُضع مؤقتًا بعد البند 16 بعلامة. كما أن الفقرة (ب) (قرار 418) تحيل إلى أرقام بنود قائمة 1435 (4..9 و13 و1)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -5403,8 +5827,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/750bf502-86c2-4928-bdb9-a9a700f1ff3b/1</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 469 أحلّ نصًا كاملًا محل الفقرة (1)، وإحلال «وزارة الطاقة» في (و) محدد. لكن القرار 693 يضيف ممثل وزارة الصناعة والثروة المعدنية، والقرار 745 يضيف ممثل الهيئة السعودية للمدن الصناعية ومناطق التق)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5476,8 +5908,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/2734fa93-a1a6-4c38-8e0d-a9a700f1e46f/1</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (ناقص: (1) صورة قرار مجلس الوزراء رقم (72) وتاريخ 1434/3/16هـ غير موجودة ونصه غير وارد في new_text_in_note؛ (2) الأداة/الأدوات التي أدخلت عبارة «ممثل لوزارة الطاقة والصناعة والثروة المعدنية» في المادة )</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -5564,8 +6004,25 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/c47e6347-4d53-4a50-b92d-a9a700f1a76d/1</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>موافق مع تصحيح</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>يكون للألفاظ والعبارات التالية المعاني المبينة أمام كل منها مالم يقتض السياق خلاف ذلك :
+المجلس: مجلس الوزراء .
+الرئيس: رئيس مجلس الإدارة .
+مجلس الإدارة: مجلس إدارة الهيئة العامة للاستثمار .
+الهيئة : الهيئة العامة للاستثمار .
+المحافظ : محافظ الهيئة العامة للاستثمار .
+المدينة الاقتصادية: الموقع الجغرافي الذي تصدر موافقة المجلس على إنشائه وتطويره من قبل القطاع الخاص بوصفه مدينة اقتصادية.
+اللائحة : اللائحة التنفيذية لهذا التنظيم .
+الوزير: وزير التجارة والاستثمار
+الوزارة: وزارة التجارة والاستثمار</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -5636,8 +6093,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/216a2b6e-911e-4223-a11b-adab00c670a1/1</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 234 واضح: يصير البند 1 «1- المحافظ  عضواً.». لكن القرار 653 يضيف «ممثل من وزارة الطاقة» دون رقم بند ولا موضع، وhk_text ما زال فيه البند 5 «ممثل من وزارة الطاقة والصناعة والثروة المعدنية»، فلا ي)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -5733,8 +6198,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/9a1c4977-c539-4e01-8c88-a9a700f2efa9/1</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 586 أحلّ نصًا كاملًا محل الفقرة (1) (أ إلى ك)، فهي معلومة حرفيًا. لكن القرار 382 أضاف «ممثل من وزارة الطاقة» دون تحديد حرف البند ولا صياغته، وأمر بإعادة الترتيب، فموضع الإضافة غير محدد. كذلك hk)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5806,8 +6279,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/16c49913-599f-406b-b016-a9a700f172c9/1</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 590 قابل للتطبيق تمامًا. لكن القرار 586 يُحل «الهيئة العامة للطرق» محل «وزارة النقل والخدمات اللوجستية» في الفقرة (2)، وهذه العبارة غير موجودة في النص (فيه «وزارة الموصلات»)؛ أداة تغيير المسمى )</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -5880,8 +6361,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/90b81287-baab-4f66-a9c1-a9a700f2ce78/1</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (لا يمكن تركيب النص الساري الكامل لسببين: (1) hk_text وboe_body مبتوران، فلا يحويان إلا صدر الفقرة (أ)، والتعديلات تمس قائمة الأعضاء والفقرات (ب) و(د) غير الموجودة في النص. (2) القرار 790 يضيف فقرة فرع)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -5952,8 +6441,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/a122634e-98ea-4e40-b4dd-ab5700c51c7d/1</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 618 يضيف «ممثل من المركز الوطني لتنمية القطاع غير الربحي» إلى عضوية اللجنة، دون تحديد موضعه في القائمة غير المرقمة ولا صياغة البند. النص الناقص الوحيد هو هذا العضو. المقترح للمالك: يُدرج «ممثل )</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6029,8 +6526,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/cad66e4d-38d3-4baa-8049-a9a700f1e7a8/1</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (المرسوم م/190 يضيف تعريف «المجلس: مجلس إدارة الهيئة» دون تحديد موضعه ولا رقم فقرته؛ وُضع مؤقتًا في آخر المادة بعلامة [موضع الإضافة غير محدد في الأداة] ويلزم قرار المالك في الموضع والترقيم. كذلك نص م/1)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -6130,8 +6635,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/cad66e4d-38d3-4baa-8049-a9a700f1e7a8/1</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (م/190 يضيف «الرئيس التنفيذي للهيئة عضواً» دون تحديد موضعه ويأمر بـ«تعديل ترتيب الفقرات تبعاً لذلك»؛ وُضع العضو مؤقتًا بعد (ط) بعلامة، ولم يُعَد ترقيم الحروف (حُذفت ج وبقيت د..ط كما هي) — يلزم قرار الم)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -6202,8 +6715,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/dd7a7d7d-a92d-431b-9ec3-a9a700f28a46/1</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (القرار 693 يفترض نصًا فيه «ممثل من وزارة الطاقة والصناعة والثروة المعدنية»، ونص حكيم والهيئة كلاهما بالتشكيل الوزاري القديم؛ الأداة الوسيطة التي أعادت تشكيل المجلس ناقصة (تُجلب أولًا). وحتى بعد جلبها،)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -6278,8 +6799,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/b19a8aa6-7b50-43f0-ab8c-a9a700f1a446/1</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (نص المادة (6) نفسه ساري كما في hk_text (final_text = hk_text بلا تغيير). لكن الملاحظة المفتوحة تخص نصًا أضافه المرسوم م/5 إلى النظام دون رقم مادة ولا موضع (وضعته الهيئة تحت المادة 6)؛ موضع إدراجه في ح)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -6357,8 +6886,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/ae482429-33b8-4e3f-a3ae-a9a700f23d5c/1</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (الفقرة (6) قائمة نظامًا (عدّلها م/64 والقرار 419) لكن نصها الكامل غير موجود في hk_text ولا في الصور ولا الملاحظات (يرد مختصرًا «... اللائحة التنفيذية ...»)، كما أن الأداة الوسيطة التي أحلّت «وزير المو)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6433,8 +6970,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/e4436403-31ee-439c-bac4-a9a700f2a17d/1</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>موافق مع تصحيح</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>1 - إذا تبين للوزارة أن شخصاً خالف أيًّا من أحكام النظام أو اللائحة التنفيذية أو اللوائح أو شروط الرخصة أو التعليمات أو القرارات التي يصدرها الوزير، أو شرع في ذلك، فيجب عليها في الحالات العاجلة والضرورية - بقرار يصدر من الوزير - أن تتخذ واحداً أو أكثر مما يأتي: أ - إلزامه بالتوقف عن الاستمرار في المخالفة.ب - إلزامه بإصلاح الوضع واتخاذ الإجراءات التصحيحية اللازمة لمعالجة نتائج المخالفة، فإن تأخر فللوزارة أن تقوم بذلك على نفقته.ج - إيقاف النشاط المرخص به جزئيًّا أو كليًّا بما لا يتجاوز (ستة) أشهر.د - اتخاذ ما يلزم لإدارة أيٍّ من أوجه النشاط المرخص به مؤقتاً لمدة محددة لا تتجاوز (ستة) أشهر قابلة للتجديد مرة واحدة، بما يكفل ضمان استمرار ذلك النشاط، وفقاً للقواعد والإجراءات التي تحددها اللائحة التنفيذية. 2 - ينفذ القرار الصادر في هذا الشأن من تاريخ إبلاغ المخالف به، على أن تحيل الوزارة المخالفة خلال (عشرة) أيام عمل إلى اللجنة - المشار إليها في الفقرة (1) من المادة (السابعة عشرة) من هذا النظام - للنظر فيها، وعلى اللجنة أن تُصدر قراراً في هذا الشأن خلال مدة لا تتجاوز (عشرين) يوم عمل، وإذا لم تبت اللجنة خلال هذه المدة، أو لم يقبل صاحب الشأن بما تقرره، جاز له الاعتراض أمام المحكمة الإدارية وفقاً للإجراءات النظامية المتبعة في هذا الشأن.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -6504,8 +7049,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (الأداة تعدل المقدار فقط ولا تعطي نصًا بديلًا، والنص في حكيم فقرتان (أ) و(ب) بمقدارين لرتب مختلفة؛ توحيدهما في مقدار واحد يقتضي إعادة صياغة (حذف الفقرتين أو دمجهما) لا يحددها النص. مقترح للمالك (غير مع)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -6575,8 +7128,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/8a12c94e-5a31-45cf-9c57-ac4400be8677/1</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (الأداة تعدل المقدار فقط بلا نص بديل، والنص في حكيم فيه البندان 1 و2 بمقدارين بحسب الرتبة؛ موضع الإحلال وشكله (حذف البندين أو دمجهما في عبارة واحدة) غير محدد في الأداة. الأداة لا تذكر «شهريا» صراحة. مق)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -6651,8 +7212,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/407a32f0-2e60-4c3e-9994-a9a700f2952a/1</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>موافق مع تصحيح</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>يؤسس بمُقتضى هذا النظام صندوق يُسمَّى: ( صندوق التنمية الصناعية السعوديِّ )، وتكون له الشخصية الاعتبارية، ويمثله رئيس مجلِس إدارته، ويكون مركزُه الرئيسي في مدينة الرياض، وللصندوق في سبيل مزاولة نشاطه أن يُنشئ فروعًا أو يعين وكلاء في مدن أخرى. ويرتبط الصندوق تنظيمياً بصندوق التنمية الوطني .</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -6727,8 +7296,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/407a32f0-2e60-4c3e-9994-a9a700f2952a/1</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>موافق مع تصحيح</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>رأس مال الصندوق خمسمائة مليون ريال تدفعه وزارة المالية والاقتصاد الوطني تدريجيًّا حسبما يتم الاتفاق عليه مع الصندوق، ويجوز زيادته بقرار من مجلس الوزراء.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -6798,8 +7375,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/23576008-1ce4-4685-ac3e-a9a700f2cb02/1</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (الأداة تقول «إضافة تعريف ... إلى المادة (الأولى)» بلا موضع، والصفحة 7 من المرفق (النص الموحد) تظهر أول المادة حتى «الإتاوة» فقط مع حاشية الإضافة، فلا يظهر الموضع. النصان مقروءان كاملين (منقولان في الس)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -6874,8 +7459,16 @@
           <t>https://laws.boe.gov.sa/BoeLaws/Laws/LawDetails/85eb2897-bec6-4c0c-b1d7-ac7c008ec09c/1</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>مؤجل</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 24/10/2026: «نفذ كل الخطوات وانا موافق على كل ما تريد» — مؤجل: لا نص ساري كامل قابل للتطبيق (م/101 محدد الموضع وطُبّق في draft_text (النص يكتب «الشئون» والأداة «الشؤون»، اختلاف رسم). م/76 يضيف «وزارة الصحة» إلى الجهات دون موضع ولا صيغة حرفية، فيقرر المالك موضعها (مثلًا «ووزارة الصحة» قبل «وال)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
